--- a/dealer_info.xlsx
+++ b/dealer_info.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N52"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -826,21 +826,21 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>140221</v>
+        <v>121481</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rothwell</t>
+          <t>Blacktown</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>QLD</t>
+          <t>NSW</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Northern</t>
+          <t>Eastern</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -849,22 +849,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rothwell</t>
+          <t>Blacktown</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Rothwell</t>
+          <t>Blacktown</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>QLD</t>
+          <t>NSW</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Northern</t>
+          <t>Eastern</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -874,25 +874,25 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>QLD Metro</t>
+          <t>NSW Metro</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Feb, Jan, Mar, May</t>
+          <t>Apr, Feb, Jan, Jun, Mar, May</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121481</v>
+        <v>124501</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Blacktown</t>
+          <t>Coffs Harbour</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -911,12 +911,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Blacktown</t>
+          <t>Coffs Harbour</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Blacktown</t>
+          <t>Coffs Harbour</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -931,30 +931,30 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>Regional</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>NSW Metro</t>
+          <t>NSW Regional</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Apr, Feb, Jan, Jun, Mar, May</t>
+          <t>Apr, Feb, Jan, Mar, May</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124501</v>
+        <v>128301</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Coffs Harbour</t>
+          <t>Dubbo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Coffs Harbour</t>
+          <t>Dubbo</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Coffs Harbour</t>
+          <t>Dubbo</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1003,20 +1003,20 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Apr, Feb, Jan, Mar, May</t>
+          <t>Apr, Feb, Jan, Jun, Mar, May</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128301</v>
+        <v>121701</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dubbo</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1035,12 +1035,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dubbo</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Dubbo</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1055,12 +1055,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Regional</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>NSW Regional</t>
+          <t>NSW Metro</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1074,11 +1074,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121701</v>
+        <v>120201</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Mascot</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1097,12 +1097,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Mascot</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Mascot</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1136,11 +1136,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120201</v>
+        <v>125411</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mascot</t>
+          <t>Nowra</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Mascot</t>
+          <t>Nowra</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Mascot</t>
+          <t>Nowra</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1179,30 +1179,30 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>Regional</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>NSW Metro</t>
+          <t>NSW Regional</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Apr, Feb, Jan, Jun, Mar, May</t>
+          <t>Feb, Jan</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125411</v>
+        <v>128001</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nowra</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nowra</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Nowra</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1251,20 +1251,20 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Feb, Jan</t>
+          <t>Apr, Feb, Jan, Jun, Mar, May</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128001</v>
+        <v>127501</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Penrith</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Penrith</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Penrith</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Regional</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>NSW Regional</t>
+          <t>NSW Metro</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1322,11 +1322,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127501</v>
+        <v>126201</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Penrith</t>
+          <t>Queanbeyan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Penrith</t>
+          <t>Queanbeyan</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Penrith</t>
+          <t>Queanbeyan</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1365,30 +1365,30 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>Regional</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>NSW Metro</t>
+          <t>NSW Regional</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Apr, Feb, Jan, Jun, Mar, May</t>
+          <t>Apr, Feb, Jan, Mar, May</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126201</v>
+        <v>123401</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Queanbeyan</t>
+          <t>Tamworth</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Queanbeyan</t>
+          <t>Tamworth</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Queanbeyan</t>
+          <t>Tamworth</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1437,20 +1437,20 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Apr, Feb, Jan, Mar, May</t>
+          <t>Apr, Mar, May</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123401</v>
+        <v>122591</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tamworth</t>
+          <t>Tuggerah</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tamworth</t>
+          <t>Tuggerah</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tamworth</t>
+          <t>Tuggerah</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1499,20 +1499,20 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Apr, Mar, May</t>
+          <t>Apr, Feb, Jan, Jun, Mar, May</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122591</v>
+        <v>124861</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tuggerah</t>
+          <t>Tweed Heads</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Eastern</t>
+          <t>Northern</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tuggerah</t>
+          <t>Tweed Heads</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tuggerah</t>
+          <t>Tweed Heads</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Eastern</t>
+          <t>Northern</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1561,20 +1561,20 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Apr, Feb, Jan, Jun, Mar, May</t>
+          <t>Apr, Feb, Mar</t>
         </is>
       </c>
       <c r="N22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124861</v>
+        <v>126501</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tweed Heads</t>
+          <t>Wagga Wagga</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Northern</t>
+          <t>Eastern</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tweed Heads</t>
+          <t>Wagga Wagga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tweed Heads</t>
+          <t>Wagga Wagga</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Northern</t>
+          <t>Eastern</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1623,30 +1623,30 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Apr, Feb, Mar</t>
+          <t>Feb, Mar</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126501</v>
+        <v>146701</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wagga Wagga</t>
+          <t>Bundaberg</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NSW</t>
+          <t>QLD</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Eastern</t>
+          <t>Northern</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1655,22 +1655,22 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Wagga Wagga</t>
+          <t>Bundaberg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Wagga Wagga</t>
+          <t>Bundaberg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>NSW</t>
+          <t>QLD</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Eastern</t>
+          <t>Northern</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1680,25 +1680,25 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>NSW Regional</t>
+          <t>QLD Regional</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Feb, Mar</t>
+          <t>Apr, Feb, Mar, May</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>146701</v>
+        <v>141571</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bundaberg</t>
+          <t>Capalaba</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bundaberg</t>
+          <t>Capalaba</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Bundaberg</t>
+          <t>Capalaba</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Apr, Feb, Mar, May</t>
+          <t>Apr, Feb, Jan, Mar</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -1756,11 +1756,11 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>141571</v>
+        <v>142141</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capalaba</t>
+          <t>Gold Coast</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1779,12 +1779,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Capalaba</t>
+          <t>Gold Coast</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Capalaba</t>
+          <t>Gold Coast</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1809,20 +1809,20 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Apr, Feb, Jan, Mar</t>
+          <t>Apr, Feb, Jan, Jun, Mar, May</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>142141</v>
+        <v>145701</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gold Coast</t>
+          <t>Gympie</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gold Coast</t>
+          <t>Gympie</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Gold Coast</t>
+          <t>Gympie</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1871,20 +1871,20 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Apr, Feb, Jan, Jun, Mar, May</t>
+          <t>Jun, Mar</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>145701</v>
+        <v>146551</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Gympie</t>
+          <t>Hervey Bay</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gympie</t>
+          <t>Hervey Bay</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Gympie</t>
+          <t>Hervey Bay</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1933,20 +1933,20 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Jun, Mar</t>
+          <t>Apr, Feb, Jan, Mar</t>
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>146551</v>
+        <v>141181</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hervey Bay</t>
+          <t>Hillcrest</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hervey Bay</t>
+          <t>Hillcrest</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Hervey Bay</t>
+          <t>Hillcrest</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1985,30 +1985,30 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Regional</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>QLD Regional</t>
+          <t>QLD Metro</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Apr, Feb, Jan, Mar</t>
+          <t>Feb, Jan, Jun, Mar, May</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>141181</v>
+        <v>143051</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hillcrest</t>
+          <t>Ipswich</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hillcrest</t>
+          <t>Ipswich</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Hillcrest</t>
+          <t>Ipswich</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Feb, Jan, Jun, Mar, May</t>
+          <t>Apr, Feb, Jan, Mar, May</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -2066,11 +2066,11 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>143051</v>
+        <v>145581</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ipswich</t>
+          <t>Maroochydore</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ipswich</t>
+          <t>Maroochydore</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Ipswich</t>
+          <t>Maroochydore</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2109,30 +2109,30 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>Regional</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>QLD Metro</t>
+          <t>QLD Regional</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Apr, Feb, Jan, Mar, May</t>
+          <t>Apr, Feb, Jan, May</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>145581</v>
+        <v>145061</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Maroochydore</t>
+          <t>Morayfield</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Maroochydore</t>
+          <t>Morayfield</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Maroochydore</t>
+          <t>Morayfield</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2171,30 +2171,30 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Regional</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>QLD Regional</t>
+          <t>QLD Metro</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Apr, Feb, Jan, May</t>
+          <t>Apr, Feb, Jan, Mar, May</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>145061</v>
+        <v>145601</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Morayfield</t>
+          <t>Nambour</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Morayfield</t>
+          <t>Nambour</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Morayfield</t>
+          <t>Nambour</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2233,30 +2233,30 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>Regional</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>QLD Metro</t>
+          <t>QLD Regional</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Apr, Feb, Jan, Mar, May</t>
+          <t>Apr, Jan, May</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>145601</v>
+        <v>140211</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nambour</t>
+          <t>Redcliffe</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2275,12 +2275,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nambour</t>
+          <t>Redcliffe</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Nambour</t>
+          <t>Redcliffe</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2295,30 +2295,30 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Regional</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>QLD Regional</t>
+          <t>QLD Metro</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Apr, Jan, May</t>
+          <t>Jan, Feb, Mar, Apr, May, Jun</t>
         </is>
       </c>
       <c r="N34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>140211</v>
+        <v>147001</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Redcliffe</t>
+          <t>Rockhampton</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Redcliffe</t>
+          <t>Rockhampton</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Redcliffe</t>
+          <t>Rockhampton</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>Regional</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>QLD Metro</t>
+          <t>QLD Regional</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2376,11 +2376,11 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>147001</v>
+        <v>141271</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Rockhampton</t>
+          <t>Springwood</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rockhampton</t>
+          <t>Springwood</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Rockhampton</t>
+          <t>Springwood</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2419,30 +2419,30 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Regional</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>QLD Regional</t>
+          <t>QLD Metro</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Apr, Feb, Jan, Jun, Mar, May</t>
+          <t>Apr, Feb, Jan, Mar, May</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>141271</v>
+        <v>143501</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Springwood</t>
+          <t>Toowoomba</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Springwood</t>
+          <t>Toowoomba</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Springwood</t>
+          <t>Toowoomba</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2481,30 +2481,30 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>Regional</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>QLD Metro</t>
+          <t>QLD Regional</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Apr, Feb, Jan, Mar, May</t>
+          <t>Jan, Mar</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>143501</v>
+        <v>148141</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Toowoomba</t>
+          <t>Townsville</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2523,12 +2523,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Toowoomba</t>
+          <t>Townsville</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Toowoomba</t>
+          <t>Townsville</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2553,30 +2553,30 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Jan, Mar</t>
+          <t>Apr, Feb, Jan, Mar</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>148141</v>
+        <v>150861</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Townsville</t>
+          <t>Adelaide North</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>QLD</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Northern</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2585,50 +2585,50 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Townsville</t>
+          <t>Adelaide North</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Townsville</t>
+          <t>Adelaide North</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>QLD</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Northern</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Regional</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>QLD Regional</t>
+          <t>SA Metro</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Apr, Feb, Jan, Mar</t>
+          <t>Apr, Feb, Jan, Jun, Mar, May</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>150861</v>
+        <v>151181</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Adelaide North</t>
+          <t>Gawler</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2647,12 +2647,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Adelaide North</t>
+          <t>Gawler</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Adelaide North</t>
+          <t>Gawler</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2667,40 +2667,40 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>Regional</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>SA Metro</t>
+          <t>SA Regional</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Apr, Feb, Jan, Jun, Mar, May</t>
+          <t>Apr, Feb, Jan, Mar</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>151181</v>
+        <v>136901</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Gawler</t>
+          <t>Albury Wodonga</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>VIC</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Southern</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -2709,22 +2709,22 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Gawler</t>
+          <t>Albury Wodonga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Gawler</t>
+          <t>Albury Wodonga</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>VIC</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Southern</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2734,25 +2734,25 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>SA Regional</t>
+          <t>VIC Regional</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Apr, Feb, Jan, Mar</t>
+          <t>Apr, Feb, Jan, Jun, Mar, May</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136901</v>
+        <v>133501</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Albury Wodonga</t>
+          <t>Ballarat</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Albury Wodonga</t>
+          <t>Ballarat</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Albury Wodonga</t>
+          <t>Ballarat</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2801,20 +2801,20 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Apr, Feb, Jan, Jun, Mar, May</t>
+          <t>Feb, Jan, Mar, May</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133501</v>
+        <v>135501</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ballarat</t>
+          <t>Bendigo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ballarat</t>
+          <t>Bendigo</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Ballarat</t>
+          <t>Bendigo</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Feb, Jan, Mar, May</t>
+          <t>Apr, Feb, Jan, Mar</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -2872,11 +2872,11 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135501</v>
+        <v>130831</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bendigo</t>
+          <t>Bundoora</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2895,12 +2895,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bendigo</t>
+          <t>Bundoora</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Bendigo</t>
+          <t>Bundoora</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2915,30 +2915,30 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Regional</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>VIC Regional</t>
+          <t>VIC Metro</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Apr, Feb, Jan, Mar</t>
+          <t>Apr, Feb, Jan, Jun, Mar, May</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130831</v>
+        <v>135001</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bundoora</t>
+          <t>Mildura</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bundoora</t>
+          <t>Mildura</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Bundoora</t>
+          <t>Mildura</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2977,30 +2977,30 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>Regional</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>VIC Metro</t>
+          <t>VIC Regional</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Apr, Feb, Jan, Jun, Mar, May</t>
+          <t>Apr, Feb, Jan, May</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135001</v>
+        <v>136301</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mildura</t>
+          <t>Shepparton</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Mildura</t>
+          <t>Shepparton</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Mildura</t>
+          <t>Shepparton</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3049,20 +3049,20 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Apr, Feb, Jan, May</t>
+          <t>Apr, Feb, Jan, Jun, Mar, May</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>136301</v>
+        <v>130291</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Shepparton</t>
+          <t>Werribee</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Shepparton</t>
+          <t>Werribee</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Shepparton</t>
+          <t>Werribee</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Regional</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>VIC Regional</t>
+          <t>VIC Metro</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3120,21 +3120,21 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130291</v>
+        <v>162301</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Werribee</t>
+          <t>Bunbury</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>VIC</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Southern</t>
+          <t>Western</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -3143,50 +3143,50 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Werribee</t>
+          <t>Bunbury</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Werribee</t>
+          <t>Bunbury</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>VIC</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Southern</t>
+          <t>Western</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Metro</t>
+          <t>Regional</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>VIC Metro</t>
+          <t>WA Regional</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Apr, Feb, Jan, Jun, Mar, May</t>
+          <t>Apr, Jan, Jun, Mar, May</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>162301</v>
+        <v>160561</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bunbury</t>
+          <t>Perth - Midland</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bunbury</t>
+          <t>Perth - Midland</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Bunbury</t>
+          <t>Perth - Midland</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3225,30 +3225,30 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Regional</t>
+          <t>Metro</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>WA Regional</t>
+          <t>WA Metro</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Apr, Jan, Jun, Mar, May</t>
+          <t>Apr, Feb, Jan, Jun, Mar, May</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>160561</v>
+        <v>161001</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Perth - Midland</t>
+          <t>Perth - VicPark</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Perth - Midland</t>
+          <t>Perth - VicPark</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Perth - Midland</t>
+          <t>Perth - VicPark</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3297,20 +3297,20 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Apr, Feb, Jan, Jun, Mar, May</t>
+          <t>Apr, Feb, Jan, Mar</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>161001</v>
+        <v>160651</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Perth - VicPark</t>
+          <t>Perth - Wanneroo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Perth - VicPark</t>
+          <t>Perth - Wanneroo</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Perth - VicPark</t>
+          <t>Perth - Wanneroo</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3359,72 +3359,10 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Apr, Feb, Jan, Mar</t>
+          <t>Feb, Jan, Jun, May</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>160651</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Perth - Wanneroo</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>WA</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Western</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="b">
-        <v>0</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Perth - Wanneroo</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Perth - Wanneroo</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>WA</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Western</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Metro</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>WA Metro</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>Feb, Jan, Jun, May</t>
-        </is>
-      </c>
-      <c r="N52" t="n">
         <v>4</v>
       </c>
     </row>
